--- a/Team-Data/2014-15/3-7-2014-15.xlsx
+++ b/Team-Data/2014-15/3-7-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
         <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>0.79</v>
+        <v>0.803</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
       </c>
       <c r="I2" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="J2" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L2" t="n">
         <v>9.9</v>
@@ -691,28 +758,28 @@
         <v>25.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.382</v>
+        <v>0.381</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P2" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="n">
         <v>0.777</v>
       </c>
       <c r="R2" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T2" t="n">
         <v>41.1</v>
       </c>
       <c r="U2" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="V2" t="n">
         <v>14.4</v>
@@ -727,28 +794,28 @@
         <v>4.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.4</v>
+        <v>102.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
         <v>25</v>
@@ -772,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP2" t="n">
         <v>18</v>
@@ -784,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
         <v>27</v>
@@ -793,13 +860,13 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -808,10 +875,10 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>20</v>
@@ -933,7 +1000,7 @@
         <v>20</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -951,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
@@ -969,13 +1036,13 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
@@ -1127,10 +1194,10 @@
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN4" t="n">
         <v>27</v>
@@ -1139,7 +1206,7 @@
         <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
         <v>19</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
         <v>5</v>
@@ -1318,7 +1385,7 @@
         <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
         <v>15</v>
@@ -1351,7 +1418,7 @@
         <v>23</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -1470,25 +1537,25 @@
         <v>3</v>
       </c>
       <c r="AE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG6" t="n">
         <v>9</v>
       </c>
-      <c r="AF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
         <v>8</v>
       </c>
-      <c r="AH6" t="n">
-        <v>9</v>
-      </c>
       <c r="AI6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ6" t="n">
         <v>16</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
@@ -1515,7 +1582,7 @@
         <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
         <v>14</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -1571,34 +1638,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.615</v>
+        <v>0.609</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J7" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L7" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M7" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="N7" t="n">
         <v>0.354</v>
@@ -1607,10 +1674,10 @@
         <v>18.3</v>
       </c>
       <c r="P7" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R7" t="n">
         <v>11.3</v>
@@ -1631,7 +1698,7 @@
         <v>7.4</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y7" t="n">
         <v>4.7</v>
@@ -1643,34 +1710,34 @@
         <v>20.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.5</v>
+        <v>102.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ7" t="n">
         <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1685,7 +1752,7 @@
         <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>17</v>
@@ -1697,16 +1764,16 @@
         <v>22</v>
       </c>
       <c r="AT7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
         <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.635</v>
+        <v>0.625</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,19 +1838,19 @@
         <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85.8</v>
+        <v>85.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O8" t="n">
         <v>16.5</v>
@@ -1792,22 +1859,22 @@
         <v>21.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T8" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U8" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V8" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
@@ -1822,28 +1889,28 @@
         <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.6</v>
+        <v>104.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
         <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1855,7 +1922,7 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
         <v>6</v>
@@ -1864,19 +1931,19 @@
         <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP8" t="n">
         <v>23</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT8" t="n">
         <v>23</v>
@@ -1900,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>0.349</v>
+        <v>0.355</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1953,55 +2020,55 @@
         <v>37.1</v>
       </c>
       <c r="J9" t="n">
-        <v>86.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0.429</v>
       </c>
       <c r="L9" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M9" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="N9" t="n">
         <v>0.314</v>
       </c>
       <c r="O9" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P9" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.733</v>
+        <v>0.732</v>
       </c>
       <c r="R9" t="n">
         <v>12.2</v>
       </c>
       <c r="S9" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T9" t="n">
         <v>44.7</v>
       </c>
       <c r="U9" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V9" t="n">
         <v>14.1</v>
       </c>
       <c r="W9" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" t="n">
         <v>20.8</v>
@@ -2010,10 +2077,10 @@
         <v>99.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4.5</v>
+        <v>-4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2031,7 +2098,7 @@
         <v>18</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
         <v>27</v>
@@ -2046,10 +2113,10 @@
         <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>24</v>
@@ -2058,31 +2125,31 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
       </c>
       <c r="AW9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX9" t="n">
         <v>17</v>
       </c>
-      <c r="AX9" t="n">
-        <v>16</v>
-      </c>
       <c r="AY9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,10 +2274,10 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="n">
         <v>7</v>
@@ -2249,13 +2316,13 @@
         <v>19</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
         <v>14</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2386,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="n">
         <v>23</v>
@@ -2416,10 +2483,10 @@
         <v>25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -2496,34 +2563,34 @@
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>84.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
       </c>
       <c r="L12" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="M12" t="n">
         <v>33.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O12" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
         <v>31.7</v>
@@ -2532,10 +2599,10 @@
         <v>43.8</v>
       </c>
       <c r="U12" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V12" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="W12" t="n">
         <v>9.6</v>
@@ -2544,31 +2611,31 @@
         <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA12" t="n">
         <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
         <v>18</v>
@@ -2577,10 +2644,10 @@
         <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2604,25 +2671,25 @@
         <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT12" t="n">
         <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="n">
         <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
         <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>0.452</v>
+        <v>0.443</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L13" t="n">
         <v>6.9</v>
@@ -2693,19 +2760,19 @@
         <v>20.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O13" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P13" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R13" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S13" t="n">
         <v>34.5</v>
@@ -2717,31 +2784,31 @@
         <v>21.3</v>
       </c>
       <c r="V13" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W13" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="X13" t="n">
         <v>4.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
         <v>20.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>17</v>
@@ -2750,7 +2817,7 @@
         <v>18</v>
       </c>
       <c r="AG13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2762,10 +2829,10 @@
         <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2774,13 +2841,13 @@
         <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP13" t="n">
         <v>21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR13" t="n">
         <v>19</v>
@@ -2795,13 +2862,13 @@
         <v>18</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2935,13 +3002,13 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2992,7 +3059,7 @@
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>0.267</v>
+        <v>0.262</v>
       </c>
       <c r="H15" t="n">
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>86.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M15" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N15" t="n">
         <v>0.346</v>
       </c>
       <c r="O15" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P15" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.9</v>
@@ -3087,25 +3154,25 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
         <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3126,34 +3193,34 @@
         <v>5</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM15" t="n">
         <v>24</v>
       </c>
-      <c r="AM15" t="n">
-        <v>23</v>
-      </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
         <v>11</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3171,13 +3238,13 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
         <v>23</v>
       </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" t="n">
         <v>44</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.71</v>
+        <v>0.721</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
       </c>
       <c r="I16" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J16" t="n">
-        <v>82.8</v>
+        <v>83</v>
       </c>
       <c r="K16" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
         <v>15.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="O16" t="n">
         <v>18.3</v>
       </c>
       <c r="P16" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.774</v>
+        <v>0.777</v>
       </c>
       <c r="R16" t="n">
         <v>10.4</v>
@@ -3260,19 +3327,19 @@
         <v>42.8</v>
       </c>
       <c r="U16" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V16" t="n">
         <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X16" t="n">
         <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Z16" t="n">
         <v>19</v>
@@ -3281,13 +3348,13 @@
         <v>20.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,13 +3366,13 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3323,22 +3390,22 @@
         <v>5</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
         <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT16" t="n">
         <v>19</v>
       </c>
       <c r="AU16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV16" t="n">
         <v>6</v>
@@ -3350,7 +3417,7 @@
         <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
@@ -3359,7 +3426,7 @@
         <v>13</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BC16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" t="n">
         <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>0.452</v>
+        <v>0.443</v>
       </c>
       <c r="H17" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J17" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -3421,25 +3488,25 @@
         <v>20.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O17" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P17" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0.744</v>
       </c>
       <c r="R17" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
         <v>29.8</v>
       </c>
       <c r="T17" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="U17" t="n">
         <v>20.1</v>
@@ -3448,7 +3515,7 @@
         <v>14.8</v>
       </c>
       <c r="W17" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X17" t="n">
         <v>4.3</v>
@@ -3460,16 +3527,16 @@
         <v>19.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3478,10 +3545,10 @@
         <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI17" t="n">
         <v>29</v>
@@ -3490,22 +3557,22 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL17" t="n">
         <v>18</v>
       </c>
       <c r="AM17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN17" t="n">
         <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV17" t="n">
         <v>21</v>
@@ -3538,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
         <v>29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.532</v>
+        <v>0.525</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3597,22 +3664,22 @@
         <v>0.46</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M18" t="n">
         <v>18.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O18" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="R18" t="n">
         <v>10.1</v>
@@ -3630,13 +3697,13 @@
         <v>16.8</v>
       </c>
       <c r="W18" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X18" t="n">
         <v>4.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z18" t="n">
         <v>22.1</v>
@@ -3645,22 +3712,22 @@
         <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>11</v>
@@ -3675,7 +3742,7 @@
         <v>5</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
         <v>25</v>
@@ -3684,13 +3751,13 @@
         <v>3</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP18" t="n">
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
         <v>24</v>
@@ -3708,7 +3775,7 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
         <v>13</v>
@@ -3717,13 +3784,13 @@
         <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA18" t="n">
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
         <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>0.23</v>
+        <v>0.217</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="J19" t="n">
         <v>84.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.331</v>
+        <v>0.329</v>
       </c>
       <c r="O19" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="R19" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S19" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T19" t="n">
         <v>41.9</v>
       </c>
       <c r="U19" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V19" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
         <v>8.4</v>
@@ -3821,19 +3888,19 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA19" t="n">
         <v>21.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>98</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7.7</v>
+        <v>-7.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3845,13 +3912,13 @@
         <v>28</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3863,7 +3930,7 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3872,7 +3939,7 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
         <v>4</v>
@@ -3884,10 +3951,10 @@
         <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
         <v>8</v>
@@ -3905,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -3952,52 +4019,52 @@
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.7</v>
+        <v>83</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O20" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.771</v>
+        <v>0.764</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="S20" t="n">
         <v>31.9</v>
       </c>
       <c r="T20" t="n">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
       <c r="U20" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="W20" t="n">
         <v>6.8</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,16 +4073,16 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4027,22 +4094,22 @@
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>23</v>
       </c>
       <c r="AM20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN20" t="n">
         <v>8</v>
@@ -4054,19 +4121,19 @@
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
         <v>19</v>
       </c>
       <c r="AT20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU20" t="n">
         <v>16</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>15</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4075,7 +4142,7 @@
         <v>26</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -4119,49 +4186,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
         <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>0.197</v>
+        <v>0.2</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J21" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.431</v>
+        <v>0.432</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
       </c>
       <c r="M21" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O21" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="P21" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="Q21" t="n">
         <v>0.771</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
         <v>29.5</v>
@@ -4170,7 +4237,7 @@
         <v>40.3</v>
       </c>
       <c r="U21" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V21" t="n">
         <v>14.4</v>
@@ -4185,19 +4252,19 @@
         <v>4.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="AC21" t="n">
         <v>-8.699999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4221,13 +4288,13 @@
         <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4251,7 +4318,7 @@
         <v>17</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW21" t="n">
         <v>23</v>
@@ -4263,7 +4330,7 @@
         <v>7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BA21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -4379,22 +4446,22 @@
         <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
         <v>6</v>
@@ -4415,16 +4482,16 @@
         <v>7</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
         <v>3</v>
       </c>
       <c r="AS22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" t="n">
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G23" t="n">
-        <v>0.323</v>
+        <v>0.317</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J23" t="n">
         <v>81.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O23" t="n">
         <v>14.1</v>
@@ -4522,31 +4589,31 @@
         <v>19.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R23" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>40.7</v>
+        <v>40.9</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
         <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21.3</v>
@@ -4555,13 +4622,13 @@
         <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-5.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4573,19 +4640,19 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ23" t="n">
         <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4606,7 +4673,7 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
@@ -4615,7 +4682,7 @@
         <v>26</v>
       </c>
       <c r="AV23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
@@ -4624,10 +4691,10 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F24" t="n">
         <v>49</v>
       </c>
       <c r="G24" t="n">
-        <v>0.222</v>
+        <v>0.21</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4683,79 +4750,79 @@
         <v>33.1</v>
       </c>
       <c r="J24" t="n">
-        <v>81</v>
+        <v>80.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.409</v>
+        <v>0.41</v>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M24" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.32</v>
+        <v>0.319</v>
       </c>
       <c r="O24" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P24" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.68</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S24" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T24" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U24" t="n">
         <v>20.5</v>
       </c>
       <c r="V24" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="W24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X24" t="n">
         <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB24" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10.1</v>
+        <v>-10.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG24" t="n">
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4776,16 +4843,16 @@
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>0.516</v>
+        <v>0.524</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="J25" t="n">
         <v>86.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L25" t="n">
         <v>9.300000000000001</v>
@@ -4880,10 +4947,10 @@
         <v>0.352</v>
       </c>
       <c r="O25" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P25" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q25" t="n">
         <v>0.774</v>
@@ -4901,7 +4968,7 @@
         <v>20.6</v>
       </c>
       <c r="V25" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W25" t="n">
         <v>8.800000000000001</v>
@@ -4916,16 +4983,16 @@
         <v>22.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.3</v>
+        <v>105.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4943,13 +5010,13 @@
         <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM25" t="n">
         <v>7</v>
@@ -4961,7 +5028,7 @@
         <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ25" t="n">
         <v>6</v>
@@ -4973,16 +5040,16 @@
         <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>23</v>
       </c>
       <c r="AV25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -4991,16 +5058,16 @@
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
         <v>41</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>0.672</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J26" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L26" t="n">
         <v>10</v>
@@ -5059,55 +5126,55 @@
         <v>27.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O26" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P26" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="R26" t="n">
         <v>10.8</v>
       </c>
       <c r="S26" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="T26" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V26" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W26" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X26" t="n">
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.4</v>
+        <v>102.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5116,16 +5183,16 @@
         <v>4</v>
       </c>
       <c r="AG26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH26" t="n">
         <v>5</v>
       </c>
-      <c r="AH26" t="n">
-        <v>7</v>
-      </c>
       <c r="AI26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>8</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>7</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>25</v>
@@ -5152,16 +5219,16 @@
         <v>17</v>
       </c>
       <c r="AS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="n">
         <v>2</v>
       </c>
-      <c r="AT26" t="n">
-        <v>3</v>
-      </c>
       <c r="AU26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW26" t="n">
         <v>25</v>
@@ -5173,13 +5240,13 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
         <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -5211,43 +5278,43 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
         <v>21</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>0.344</v>
+        <v>0.35</v>
       </c>
       <c r="H27" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I27" t="n">
         <v>36.2</v>
       </c>
       <c r="J27" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0.45</v>
       </c>
       <c r="L27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.331</v>
+        <v>0.329</v>
       </c>
       <c r="O27" t="n">
         <v>22.9</v>
       </c>
       <c r="P27" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0.773</v>
@@ -5262,10 +5329,10 @@
         <v>44.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V27" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
@@ -5277,19 +5344,19 @@
         <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="AC27" t="n">
         <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,7 +5368,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5352,10 +5419,10 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -5393,43 +5460,43 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E28" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>0.617</v>
+        <v>0.623</v>
       </c>
       <c r="H28" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I28" t="n">
         <v>38.1</v>
       </c>
       <c r="J28" t="n">
-        <v>83.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O28" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P28" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q28" t="n">
         <v>0.771</v>
@@ -5438,22 +5505,22 @@
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="V28" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W28" t="n">
         <v>7.7</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
         <v>4.7</v>
@@ -5471,28 +5538,28 @@
         <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF28" t="n">
         <v>7</v>
       </c>
       <c r="AG28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,7 +5568,7 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>18</v>
@@ -5510,7 +5577,7 @@
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
@@ -5519,13 +5586,13 @@
         <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5720,19 @@
         <v>3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>10</v>
       </c>
       <c r="AF29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
         <v>10</v>
@@ -5683,7 +5750,7 @@
         <v>9</v>
       </c>
       <c r="AN29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
         <v>4</v>
@@ -5719,10 +5786,10 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-1</v>
       </c>
       <c r="AD30" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
         <v>20</v>
@@ -5850,7 +5917,7 @@
         <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ30" t="n">
         <v>29</v>
@@ -5877,28 +5944,28 @@
         <v>25</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
         <v>15</v>
       </c>
       <c r="AU30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV30" t="n">
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ30" t="n">
         <v>8</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
@@ -5939,37 +6006,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" t="n">
         <v>35</v>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.556</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J31" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O31" t="n">
         <v>15.9</v>
@@ -5978,19 +6045,19 @@
         <v>21.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R31" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S31" t="n">
         <v>33.5</v>
       </c>
       <c r="T31" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U31" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="V31" t="n">
         <v>15.1</v>
@@ -6008,16 +6075,16 @@
         <v>21.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,10 +6096,10 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ31" t="n">
         <v>21</v>
@@ -6047,10 +6114,10 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
         <v>24</v>
@@ -6071,19 +6138,19 @@
         <v>5</v>
       </c>
       <c r="AV31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX31" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
         <v>20</v>
@@ -6092,7 +6159,7 @@
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-7-2014-15</t>
+          <t>2015-03-07</t>
         </is>
       </c>
     </row>
